--- a/AAII_Financials/Yearly/VRNS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRNS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>VRNS</t>
   </si>
@@ -1007,8 +1007,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
+      <c r="D14" s="3">
+        <v>700</v>
       </c>
       <c r="E14" s="3">
         <v>-12700</v>
@@ -1128,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>770000</v>
+        <v>769400</v>
       </c>
       <c r="E17" s="3">
         <v>668600</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-146500</v>
+        <v>-145900</v>
       </c>
       <c r="E18" s="3">
         <v>-117700</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-142100</v>
+        <v>-141500</v>
       </c>
       <c r="E21" s="3">
         <v>-108200</v>
